--- a/output/topology_excel/20094.xlsx
+++ b/output/topology_excel/20094.xlsx
@@ -487,7 +487,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" t="n">
         <v>4</v>
-      </c>
-      <c r="B12" t="n">
-        <v>5</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -704,10 +704,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="n">
         <v>11</v>
-      </c>
-      <c r="B13" t="n">
-        <v>12</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -748,10 +748,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -814,10 +814,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>1</v>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,10 +872,10 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="F20" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -883,7 +883,7 @@
         <v>1</v>
       </c>
       <c r="B21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,18 +894,18 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>323</v>
+        <v>299</v>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F22" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -927,7 +927,7 @@
         <v>2</v>
       </c>
       <c r="B23" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,10 +938,10 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>54</v>
+        <v>323</v>
       </c>
       <c r="F23" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -949,7 +949,7 @@
         <v>2</v>
       </c>
       <c r="B24" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,10 +960,10 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>299</v>
+        <v>94</v>
       </c>
       <c r="F24" t="n">
-        <v>69</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
@@ -971,7 +971,7 @@
         <v>3</v>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>3</v>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,18 +1004,18 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,10 +1026,10 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>332</v>
+        <v>446</v>
       </c>
       <c r="F27" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
@@ -1048,18 +1048,18 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>446</v>
+        <v>333</v>
       </c>
       <c r="F28" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B29" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,18 +1092,18 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>136</v>
+        <v>311</v>
       </c>
       <c r="F30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B31" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1114,15 +1114,15 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>25</v>
+        <v>182</v>
       </c>
       <c r="F31" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B32" t="n">
         <v>15</v>
@@ -1136,18 +1136,18 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>157</v>
+        <v>199</v>
       </c>
       <c r="F32" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B33" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,18 +1158,18 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>136</v>
+        <v>71</v>
       </c>
       <c r="F33" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B34" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1180,18 +1180,18 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="F34" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B35" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1202,18 +1202,18 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="F35" t="n">
-        <v>20</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B36" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1224,18 +1224,18 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>176</v>
+        <v>141</v>
       </c>
       <c r="F36" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B37" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1246,18 +1246,18 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>311</v>
+        <v>157</v>
       </c>
       <c r="F37" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B38" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="F38" t="n">
         <v>20</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B39" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1290,18 +1290,18 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F39" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B40" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F40" t="n">
         <v>14</v>
@@ -1320,10 +1320,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B41" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="F41" t="n">
         <v>15</v>
@@ -1342,10 +1342,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B42" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1356,18 +1356,18 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>199</v>
+        <v>160</v>
       </c>
       <c r="F42" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B43" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1378,40 +1378,40 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="F43" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
+        <v>9</v>
+      </c>
+      <c r="B44" t="n">
+        <v>14</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>176</v>
+      </c>
+      <c r="F44" t="n">
         <v>11</v>
-      </c>
-      <c r="B44" t="n">
-        <v>12</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" t="n">
-        <v>160</v>
-      </c>
-      <c r="F44" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B45" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1422,18 +1422,18 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="F45" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B46" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1444,15 +1444,15 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>199</v>
+        <v>110</v>
       </c>
       <c r="F46" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B47" t="n">
         <v>14</v>
@@ -1466,18 +1466,18 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="F47" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B48" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1488,40 +1488,40 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="F48" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B49" t="n">
+        <v>15</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>199</v>
+      </c>
+      <c r="F49" t="n">
         <v>18</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" t="n">
-        <v>171</v>
-      </c>
-      <c r="F49" t="n">
-        <v>62</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B50" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1532,15 +1532,15 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>176</v>
+        <v>25</v>
       </c>
       <c r="F50" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B51" t="n">
         <v>18</v>
@@ -1557,15 +1557,15 @@
         <v>157</v>
       </c>
       <c r="F51" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B52" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1576,15 +1576,15 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>232</v>
+        <v>106</v>
       </c>
       <c r="F52" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B53" t="n">
         <v>20</v>
@@ -1598,10 +1598,10 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>71</v>
+        <v>232</v>
       </c>
       <c r="F53" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/20094.xlsx
+++ b/output/topology_excel/20094.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
         </is>
       </c>
     </row>
@@ -481,6 +491,8 @@
       <c r="F2" t="n">
         <v>18</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +515,8 @@
       <c r="F3" t="n">
         <v>16</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +539,8 @@
       <c r="F4" t="n">
         <v>16</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +563,8 @@
       <c r="F5" t="n">
         <v>14</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +587,8 @@
       <c r="F6" t="n">
         <v>20</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +611,8 @@
       <c r="F7" t="n">
         <v>20</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +635,8 @@
       <c r="F8" t="n">
         <v>15</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +659,8 @@
       <c r="F9" t="n">
         <v>14</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +683,8 @@
       <c r="F10" t="n">
         <v>15</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +707,8 @@
       <c r="F11" t="n">
         <v>20</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +731,8 @@
       <c r="F12" t="n">
         <v>18</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +755,8 @@
       <c r="F13" t="n">
         <v>18</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +779,8 @@
       <c r="F14" t="n">
         <v>13</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +803,8 @@
       <c r="F15" t="n">
         <v>18</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +827,8 @@
       <c r="F16" t="n">
         <v>20</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +851,8 @@
       <c r="F17" t="n">
         <v>15</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +875,8 @@
       <c r="F18" t="n">
         <v>14</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -853,8 +897,10 @@
         <v>355</v>
       </c>
       <c r="F19" t="n">
-        <v>54</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +923,8 @@
       <c r="F20" t="n">
         <v>8</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -897,8 +945,10 @@
         <v>299</v>
       </c>
       <c r="F21" t="n">
-        <v>69</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +971,8 @@
       <c r="F22" t="n">
         <v>20</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +995,8 @@
       <c r="F23" t="n">
         <v>15</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1019,8 @@
       <c r="F24" t="n">
         <v>15</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1043,8 @@
       <c r="F25" t="n">
         <v>16</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1007,8 +1065,10 @@
         <v>332</v>
       </c>
       <c r="F26" t="n">
-        <v>46</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1031,6 +1091,8 @@
       <c r="F27" t="n">
         <v>13</v>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1053,6 +1115,8 @@
       <c r="F28" t="n">
         <v>16</v>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1075,6 +1139,8 @@
       <c r="F29" t="n">
         <v>13</v>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1097,6 +1163,8 @@
       <c r="F30" t="n">
         <v>20</v>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1119,6 +1187,8 @@
       <c r="F31" t="n">
         <v>15</v>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1141,6 +1211,8 @@
       <c r="F32" t="n">
         <v>15</v>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1163,6 +1235,8 @@
       <c r="F33" t="n">
         <v>20</v>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1185,6 +1259,8 @@
       <c r="F34" t="n">
         <v>14</v>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1199,13 +1275,19 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>171</v>
+        <v>23</v>
       </c>
       <c r="F35" t="n">
-        <v>62</v>
+        <v>14</v>
+      </c>
+      <c r="G35" t="n">
+        <v>157</v>
+      </c>
+      <c r="H35" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="36">
@@ -1229,6 +1311,8 @@
       <c r="F36" t="n">
         <v>20</v>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1251,6 +1335,8 @@
       <c r="F37" t="n">
         <v>14</v>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1273,6 +1359,8 @@
       <c r="F38" t="n">
         <v>20</v>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1295,6 +1383,8 @@
       <c r="F39" t="n">
         <v>19</v>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1317,6 +1407,8 @@
       <c r="F40" t="n">
         <v>14</v>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1339,6 +1431,8 @@
       <c r="F41" t="n">
         <v>15</v>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1361,6 +1455,8 @@
       <c r="F42" t="n">
         <v>18</v>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1383,6 +1479,8 @@
       <c r="F43" t="n">
         <v>15</v>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1405,6 +1503,8 @@
       <c r="F44" t="n">
         <v>11</v>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1427,6 +1527,8 @@
       <c r="F45" t="n">
         <v>14</v>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1449,6 +1551,8 @@
       <c r="F46" t="n">
         <v>20</v>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1471,6 +1575,8 @@
       <c r="F47" t="n">
         <v>20</v>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1493,6 +1599,8 @@
       <c r="F48" t="n">
         <v>14</v>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1515,6 +1623,8 @@
       <c r="F49" t="n">
         <v>18</v>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1537,6 +1647,8 @@
       <c r="F50" t="n">
         <v>19</v>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1559,6 +1671,8 @@
       <c r="F51" t="n">
         <v>16</v>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1581,6 +1695,8 @@
       <c r="F52" t="n">
         <v>19</v>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1603,6 +1719,8 @@
       <c r="F53" t="n">
         <v>18</v>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
